--- a/output/運営規程_いいかいご.xlsx
+++ b/output/運営規程_いいかいご.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
     <row r="54" ht="20" customHeight="1">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>（3）訪問介護員　3名以上（常勤換算2.5名以上）</t>
+          <t>（3）訪問介護員　10名（常勤7名、非常勤3名）（常勤換算2.5名以上を確保する）</t>
         </is>
       </c>
     </row>
@@ -694,14 +694,14 @@
     <row r="56" ht="20" customHeight="1">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>（4）事務職員　0名（常勤又は非常勤 0名）</t>
+          <t>（4）事務職員　1名（常勤1名）</t>
         </is>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">　　必要な事務を行う。</t>
+          <t xml:space="preserve">　　介護給付費等の請求事務及び通信連絡事務等を行う。</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>（1）営業日　月曜日から日曜日までとする。ただし、祝日、12月30日から1月3日までを除く。</t>
+          <t>（1）営業日　月曜日から金曜日までとする。ただし、祝日、8月13日から8月15日まで、12月30日から1月3日までを除く。</t>
         </is>
       </c>
     </row>
@@ -737,416 +737,423 @@
     <row r="63" ht="20" customHeight="1">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>（3）サービス提供時間　24時間（午前0時から午後12時まで）とする。</t>
+          <t>（3）サービス提供日　1月1日から1月3日までを除く毎日とする。</t>
         </is>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>（4）営業時間外は電話等により常時連絡が可能な体制とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="8" customHeight="1"/>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+          <t>（4）サービス提供時間　午前7時から午後11時までとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
+          <t>（5）営業時間外のサービス提供時間帯は、電話等により連絡が可能な体制とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="8" customHeight="1"/>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>（指定訪問介護の内容）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>第7条　事業所で行う指定訪問介護の内容は次のとおりとする。</t>
         </is>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68" s="5" t="inlineStr">
         <is>
+          <t>第7条　事業所で行う指定訪問介護の内容は次のとおりとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>（1）訪問介護計画の作成</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="32" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
-        <is>
-          <t>（2）身体介護に関する内容　①排泄・食事介助 ②清拭・入浴・身体整容 ③体位変換 ④移動・移乗介助、外出介助 ⑤その他の必要な身体の介護</t>
         </is>
       </c>
     </row>
     <row r="70" ht="32" customHeight="1">
       <c r="A70" s="5" t="inlineStr">
         <is>
+          <t>（2）身体介護に関する内容　①排泄・食事介助 ②清拭・入浴・身体整容 ③体位変換 ④移動・移乗介助、外出介助 ⑤その他の必要な身体の介護</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="32" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
           <t>（3）生活援助に関する内容　①調理 ②衣類の洗濯、補修 ③住居の掃除、整理整頓 ④生活必需品の買い物 ⑤その他必要な家事</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="8" customHeight="1"/>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72" ht="8" customHeight="1"/>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>（指定訪問介護の利用料等）</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="64" customHeight="1">
-      <c r="A73" s="5" t="inlineStr">
+    <row r="74" ht="64" customHeight="1">
+      <c r="A74" s="5" t="inlineStr">
         <is>
           <t>第8条　指定訪問介護を提供した場合の利用料の額は、介護報酬告示上の額とし、そのサービスが法定代理受領サービスであるときは、利用料のうち各利用者の負担割合に応じた額の支払いを受けるものとする。なお、法定代理受領以外の利用料については、「指定居宅サービスに要する費用の額の算定に関する基準」（平成12年2月10日厚生省告示第19号）によるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="32" customHeight="1">
-      <c r="A74" s="5" t="inlineStr">
+    <row r="75" ht="32" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>2　次条に定める通常の事業の実施地域を越えて行う事業に要する交通費は、その実費を徴収する。なお、自動車を使用した場合の交通費は、次の額とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="5" t="inlineStr">
-        <is>
-          <t>（1）事業所から片道5キロメートル未満　100円（税別）</t>
         </is>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>（2）事業所から片道5キロメートル以上　1kmを増すごとに20円ずつ加算（税別）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="32" customHeight="1">
+          <t>（1）事業所から片道5キロメートル未満　200円</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
       <c r="A77" s="5" t="inlineStr">
         <is>
+          <t>（2）事業所から片道5キロメートル以上　500円</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="32" customHeight="1">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
           <t>3　前2項の利用料等の支払を受けたときは、利用者又はその家族に対し、利用料とその他の利用料（個別の費用ごとに区分したもの）について記載した領収書を交付する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="48" customHeight="1">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>4　指定訪問介護の提供の開始に際しては、あらかじめ、利用者又はその家族に対し、当該サービスの内容及び費用に関し事前に文書で説明した上で、その内容及び支払いに同意する旨の文書に署名（記名押印）を受けるものとする。</t>
         </is>
       </c>
     </row>
     <row r="79" ht="48" customHeight="1">
       <c r="A79" s="5" t="inlineStr">
         <is>
+          <t>4　指定訪問介護の提供の開始に際しては、あらかじめ、利用者又はその家族に対し、当該サービスの内容及び費用に関し事前に文書で説明した上で、その内容及び支払いに同意する旨の文書に署名（記名押印）を受けるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="48" customHeight="1">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
           <t>5　法定代理受領サービスに該当しない指定訪問介護に係る利用料の支払いを受けたときは、提供した指定訪問介護の内容、費用の額その他必要と認められる事項を記載したサービス提供証明書を利用者に対して交付するものとする。</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="8" customHeight="1"/>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="4" t="inlineStr">
+    <row r="81" ht="8" customHeight="1"/>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>（通常の事業の実施地域）</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>第9条　通常の事業の実施地域は、大阪市とする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="8" customHeight="1"/>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="4" t="inlineStr">
+    <row r="83" ht="32" customHeight="1">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>第9条　通常の事業の実施地域は、大阪市西淀川区、淀川区、東淀川区、天王寺区、中央区、北区とする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="8" customHeight="1"/>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>（衛生管理等）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="32" customHeight="1">
-      <c r="A85" s="5" t="inlineStr">
-        <is>
-          <t>第10条　訪問介護員等の清潔の保持及び健康状態の管理を行うとともに、事業所の設備及び備品等の衛生的な管理に努めるものとする。</t>
         </is>
       </c>
     </row>
     <row r="86" ht="32" customHeight="1">
       <c r="A86" s="5" t="inlineStr">
         <is>
+          <t>第10条　訪問介護員等の清潔の保持及び健康状態の管理を行うとともに、事業所の設備及び備品等の衛生的な管理に努めるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="32" customHeight="1">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
           <t>2　事業所は、感染症の予防及びまん延の防止のため、感染対策委員会の開催（おおむね6か月に1回以上）、指針の整備、研修及び訓練の実施を行う。</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="8" customHeight="1"/>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="4" t="inlineStr">
+    <row r="88" ht="8" customHeight="1"/>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>（緊急時等における対応方法）</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="48" customHeight="1">
-      <c r="A89" s="5" t="inlineStr">
+    <row r="90" ht="48" customHeight="1">
+      <c r="A90" s="5" t="inlineStr">
         <is>
           <t>第11条　訪問介護員等は、指定訪問介護の提供を行っているときに利用者に病状の急変、その他緊急事態が生じたときは、速やかに主治医に連絡する等の措置を講じるとともに、管理者に報告する。また、主治医への連絡が困難な場合は、緊急搬送等の必要な措置を講じるものとする。</t>
-        </is>
-      </c>
-    </row>
-    <row r="90" ht="32" customHeight="1">
-      <c r="A90" s="5" t="inlineStr">
-        <is>
-          <t>2　指定訪問介護の提供により事故が発生した場合は、利用者の所在する市町村、利用者の家族、利用者に係る居宅介護支援事業者等に連絡するとともに、必要な措置を講じるものとする。</t>
         </is>
       </c>
     </row>
     <row r="91" ht="32" customHeight="1">
       <c r="A91" s="5" t="inlineStr">
         <is>
+          <t>2　指定訪問介護の提供により事故が発生した場合は、利用者の所在する市町村、利用者の家族、利用者に係る居宅介護支援事業者等に連絡するとともに、必要な措置を講じるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="32" customHeight="1">
+      <c r="A92" s="5" t="inlineStr">
+        <is>
           <t>3　利用者に対する指定訪問介護の提供により賠償すべき事故が発生した場合には、損害賠償を速やかに行うものとする。</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="8" customHeight="1"/>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="93" ht="8" customHeight="1"/>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>（苦情処理）</t>
         </is>
       </c>
     </row>
-    <row r="94" ht="32" customHeight="1">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="95" ht="32" customHeight="1">
+      <c r="A95" s="5" t="inlineStr">
         <is>
           <t>第12条　指定訪問介護の提供に係る利用者及びその家族からの苦情に迅速かつ適切に対応するために必要な措置を講じるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="64" customHeight="1">
-      <c r="A95" s="5" t="inlineStr">
+    <row r="96" ht="64" customHeight="1">
+      <c r="A96" s="5" t="inlineStr">
         <is>
           <t>2　事業所は、提供した指定訪問介護に関し、介護保険法第23条の規定により市町村が行う文書その他の物件の提出若しくは提示の求め又は当該市町村の職員からの質問若しくは照会に応じ、及び市町村が行う調査に協力するとともに、市町村から指導又は助言を受けた場合は、当該指導又は助言に従って必要な改善を行うものとする。</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="48" customHeight="1">
-      <c r="A96" s="5" t="inlineStr">
+    <row r="97" ht="48" customHeight="1">
+      <c r="A97" s="5" t="inlineStr">
         <is>
           <t>3　事業所は、提供した指定訪問介護に係る利用者からの苦情に関して国民健康保険団体連合会が行う調査に協力するとともに、国民健康保険団体連合会から指導又は助言を受けた場合は、当該指導又は助言に従って必要な改善を行うものとする。</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="8" customHeight="1"/>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98" ht="8" customHeight="1"/>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>（個人情報の保護）</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="48" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
-        <is>
-          <t>第13条　事業所は、利用者の個人情報について「個人情報の保護に関する法律」及び厚生労働省が策定した「医療・介護関係事業者における個人情報の適切な取扱いのためのガイダンス」を遵守し適切な取り扱いに努めるものとする。</t>
         </is>
       </c>
     </row>
     <row r="100" ht="48" customHeight="1">
       <c r="A100" s="5" t="inlineStr">
         <is>
+          <t>第13条　事業所は、利用者の個人情報について「個人情報の保護に関する法律」及び厚生労働省が策定した「医療・介護関係事業者における個人情報の適切な取扱いのためのガイダンス」を遵守し適切な取り扱いに努めるものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="48" customHeight="1">
+      <c r="A101" s="5" t="inlineStr">
+        <is>
           <t>2　事業者が得た利用者又はその家族の個人情報については、事業者での介護サービスの提供以外の目的では原則的に利用しないものとし、外部への情報提供については必要に応じて利用者又はその代理人の了解を得るものとする。</t>
         </is>
       </c>
     </row>
-    <row r="101" ht="8" customHeight="1"/>
-    <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="4" t="inlineStr">
+    <row r="102" ht="8" customHeight="1"/>
+    <row r="103" ht="20" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>（虐待防止に関する事項）</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="5" t="inlineStr">
-        <is>
-          <t>第14条　事業所は、利用者の人権の擁護・虐待等の防止のため次の措置を講ずるものとする。</t>
         </is>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>（1）虐待防止のための対策を検討する委員会の定期的な開催と、その結果の従業者への周知</t>
+          <t>第14条　事業所は、利用者の人権の擁護・虐待等の防止のため次の措置を講ずるものとする。</t>
         </is>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>（2）虐待防止のための指針の整備</t>
+          <t>（1）虐待防止のための対策を検討する委員会の定期的な開催と、その結果の従業者への周知</t>
         </is>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>（3）虐待を防止するための従業者に対する研修の実施（年1回以上及び新規採用時）</t>
+          <t>（2）虐待防止のための指針の整備</t>
         </is>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>（4）前3号の措置を適切に実施するための担当者の設置（虐待防止責任者：管理者）</t>
+          <t>（3）虐待を防止するための従業者に対する研修の実施（年1回以上及び新規採用時）</t>
         </is>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>（5）利用者及びその家族からの苦情処理体制の整備</t>
+          <t>（4）前3号の措置を適切に実施するための担当者の設置（虐待防止責任者：管理者）</t>
         </is>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109" s="5" t="inlineStr">
         <is>
+          <t>（5）利用者及びその家族からの苦情処理体制の整備</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="20" customHeight="1">
+      <c r="A110" s="5" t="inlineStr">
+        <is>
           <t>（6）その他虐待防止のために必要な措置</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="48" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="111" ht="48" customHeight="1">
+      <c r="A111" s="5" t="inlineStr">
         <is>
           <t>2　事業所は、サービス提供中に、当該事業所従業者又は養護者（利用者の家族等高齢者を現に養護する者）による虐待を受けたと思われる利用者を発見した場合は、速やかに、これを市町村に通報するものとする。</t>
         </is>
       </c>
     </row>
-    <row r="111" ht="8" customHeight="1"/>
-    <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="4" t="inlineStr">
+    <row r="112" ht="8" customHeight="1"/>
+    <row r="113" ht="20" customHeight="1">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>（身体拘束等の禁止）</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="32" customHeight="1">
-      <c r="A113" s="5" t="inlineStr">
-        <is>
-          <t>第15条　事業所は、利用者又は他の利用者等の生命又は身体を保護するため緊急やむを得ない場合を除き、身体的拘束その他利用者の行動を制限する行為を行わない。</t>
         </is>
       </c>
     </row>
     <row r="114" ht="32" customHeight="1">
       <c r="A114" s="5" t="inlineStr">
         <is>
+          <t>第15条　事業所は、利用者又は他の利用者等の生命又は身体を保護するため緊急やむを得ない場合を除き、身体的拘束その他利用者の行動を制限する行為を行わない。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="32" customHeight="1">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
           <t>2　緊急やむを得ず身体的拘束等を行う場合には、その態様及び時間、その際の利用者の心身の状況並びに緊急やむを得ない理由を記録する。</t>
         </is>
       </c>
     </row>
-    <row r="115" ht="8" customHeight="1"/>
-    <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="4" t="inlineStr">
+    <row r="116" ht="8" customHeight="1"/>
+    <row r="117" ht="20" customHeight="1">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>（業務継続計画の策定等）</t>
         </is>
       </c>
     </row>
-    <row r="117" ht="48" customHeight="1">
-      <c r="A117" s="5" t="inlineStr">
+    <row r="118" ht="48" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>第16条　事業所は、感染症や非常災害の発生時において、利用者に対する指定訪問介護の提供を継続的に実施し、及び非常時の体制で早期の業務再開を図るための業務継続計画を策定し、当該計画に従い必要な措置を講じる。</t>
         </is>
       </c>
     </row>
-    <row r="118" ht="32" customHeight="1">
-      <c r="A118" s="5" t="inlineStr">
+    <row r="119" ht="32" customHeight="1">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>2　事業所は、従業者に対し、業務継続計画について周知するとともに、必要な研修及び訓練を定期的に実施する。</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="8" customHeight="1"/>
-    <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="120" ht="8" customHeight="1"/>
+    <row r="121" ht="20" customHeight="1">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>（その他運営に関する重要事項）</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="32" customHeight="1">
-      <c r="A121" s="5" t="inlineStr">
+    <row r="122" ht="32" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>第17条　事業所は、従業者の資質向上のために次のとおり研修の機会を設けるものとし、また、業務の執行体制についても検証、整備する。</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="5" t="inlineStr">
-        <is>
-          <t>（1）採用時研修　採用後1か月以内</t>
         </is>
       </c>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>（2）継続研修　年2回</t>
+          <t>（1）採用時研修　採用後1か月以内</t>
         </is>
       </c>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124" s="5" t="inlineStr">
         <is>
+          <t>（2）継続研修　年2回</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
           <t>2　従業者は、業務上知り得た利用者又はその家族の秘密を保持する。</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="48" customHeight="1">
-      <c r="A125" s="5" t="inlineStr">
+    <row r="126" ht="48" customHeight="1">
+      <c r="A126" s="5" t="inlineStr">
         <is>
           <t>3　事業所は、従業者であった者に、業務上知り得た利用者又はその家族の秘密を保持させるため、従業者でなくなった後においてもこれらの秘密を保持するべき旨を、従業者との雇用契約の内容とする。</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="127" ht="20" customHeight="1">
+      <c r="A127" s="5" t="inlineStr">
         <is>
           <t>4　事業所は、職場におけるハラスメントの防止のための方針の明確化等の必要な措置を講じる。</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="32" customHeight="1">
-      <c r="A127" s="5" t="inlineStr">
-        <is>
-          <t>5　事業所は、指定訪問介護に関する諸記録を整備し、そのサービス提供をした日から最低5年間は保存するものとする。</t>
         </is>
       </c>
     </row>
     <row r="128" ht="32" customHeight="1">
       <c r="A128" s="5" t="inlineStr">
         <is>
+          <t>5　事業所は、指定訪問介護に関する諸記録を整備し、そのサービス提供をした日から最低5年間は保存するものとする。</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="32" customHeight="1">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
           <t>6　この規程に定める事項の外、運営に関する重要事項は株式会社dhpケアマネジメントと事業所の管理者との協議に基づいて定めるものとする。</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="8" customHeight="1"/>
-    <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="4" t="inlineStr">
+    <row r="130" ht="8" customHeight="1"/>
+    <row r="131" ht="20" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>附則</t>
         </is>
       </c>
     </row>
-    <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="5" t="inlineStr">
+    <row r="132" ht="20" customHeight="1">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>この規程は、令和8年2月1日から施行する。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="92">
+  <mergeCells count="93">
     <mergeCell ref="A39:E39"/>
     <mergeCell ref="A48:E48"/>
     <mergeCell ref="A1:E1"/>
@@ -1154,6 +1161,8 @@
     <mergeCell ref="A94:E94"/>
     <mergeCell ref="A103:E103"/>
     <mergeCell ref="A79:E79"/>
+    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="A65:E65"/>
     <mergeCell ref="A128:E128"/>
     <mergeCell ref="A37:E37"/>
     <mergeCell ref="A46:E46"/>
@@ -1162,29 +1171,33 @@
     <mergeCell ref="A26:E26"/>
     <mergeCell ref="A57:E57"/>
     <mergeCell ref="A113:E113"/>
+    <mergeCell ref="A71:E71"/>
+    <mergeCell ref="A129:E129"/>
     <mergeCell ref="A91:E91"/>
     <mergeCell ref="A131:E131"/>
     <mergeCell ref="A100:E100"/>
     <mergeCell ref="A52:E52"/>
     <mergeCell ref="A63:E63"/>
-    <mergeCell ref="A93:E93"/>
-    <mergeCell ref="A130:E130"/>
+    <mergeCell ref="A115:E115"/>
     <mergeCell ref="A77:E77"/>
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A83:E83"/>
     <mergeCell ref="A49:E49"/>
+    <mergeCell ref="A132:E132"/>
     <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A119:E119"/>
     <mergeCell ref="A69:E69"/>
     <mergeCell ref="A78:E78"/>
     <mergeCell ref="A118:E118"/>
     <mergeCell ref="A75:E75"/>
-    <mergeCell ref="A120:E120"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="A55:E55"/>
     <mergeCell ref="A95:E95"/>
     <mergeCell ref="A104:E104"/>
     <mergeCell ref="A32:E32"/>
+    <mergeCell ref="A97:E97"/>
     <mergeCell ref="A106:E106"/>
     <mergeCell ref="A29:E29"/>
-    <mergeCell ref="A81:E81"/>
     <mergeCell ref="A96:E96"/>
     <mergeCell ref="A31:E31"/>
     <mergeCell ref="A40:E40"/>
@@ -1197,16 +1210,12 @@
     <mergeCell ref="A124:E124"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A108:E108"/>
-    <mergeCell ref="A84:E84"/>
-    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A50:E50"/>
     <mergeCell ref="A86:E86"/>
     <mergeCell ref="A42:E42"/>
     <mergeCell ref="A47:E47"/>
     <mergeCell ref="A122:E122"/>
     <mergeCell ref="A125:E125"/>
-    <mergeCell ref="A72:E72"/>
-    <mergeCell ref="A112:E112"/>
     <mergeCell ref="A121:E121"/>
     <mergeCell ref="A13:E13"/>
     <mergeCell ref="A44:E44"/>
@@ -1215,11 +1224,9 @@
     <mergeCell ref="A114:E114"/>
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A64:E64"/>
-    <mergeCell ref="A98:E98"/>
     <mergeCell ref="A51:E51"/>
     <mergeCell ref="A107:E107"/>
     <mergeCell ref="A61:E61"/>
-    <mergeCell ref="A88:E88"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="A54:E54"/>
     <mergeCell ref="A41:E41"/>
@@ -1228,17 +1235,18 @@
     <mergeCell ref="A74:E74"/>
     <mergeCell ref="A56:E56"/>
     <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A101:E101"/>
     <mergeCell ref="A76:E76"/>
     <mergeCell ref="A33:E33"/>
     <mergeCell ref="A85:E85"/>
-    <mergeCell ref="A116:E116"/>
     <mergeCell ref="A126:E126"/>
     <mergeCell ref="A53:E53"/>
     <mergeCell ref="A109:E109"/>
     <mergeCell ref="A62:E62"/>
     <mergeCell ref="A68:E68"/>
-    <mergeCell ref="A102:E102"/>
     <mergeCell ref="A117:E117"/>
+    <mergeCell ref="A111:E111"/>
+    <mergeCell ref="A92:E92"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
